--- a/Sales-Klantservice/Peer_Sprint_4/Jurrian_Groep1_team3_sales_en_klantenservice_sprint4.xlsx
+++ b/Sales-Klantservice/Peer_Sprint_4/Jurrian_Groep1_team3_sales_en_klantenservice_sprint4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jurri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{745DD476-9E3E-4645-B09A-5E9B1169B402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA61A9FC-AFC2-4FE2-B53B-BDC3B028D5D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F36616B-C394-4612-9F9B-1D401A00BD80}"/>
   </bookViews>
@@ -131,13 +131,13 @@
     <t xml:space="preserve"> Realistisch gezien zouden de punten door 1,5 of 2 gedeeld moeten worden</t>
   </si>
   <si>
-    <t>planning taken gemaakt</t>
-  </si>
-  <si>
-    <t>use case feedback verwerkt</t>
-  </si>
-  <si>
     <t>hoofdprocessen gemaakt, wireframe gemaakt klantensysteem, header en footer voor website met Joeri, loginpagina gemaakt</t>
+  </si>
+  <si>
+    <t>use case feedback verwerkt, userstories gemaakt</t>
+  </si>
+  <si>
+    <t>planning taken gemaakt (laat maar)</t>
   </si>
 </sst>
 </file>
@@ -948,10 +948,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="8">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:5" s="4" customFormat="1" ht="40.049999999999997" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -965,7 +965,7 @@
         <v>17</v>
       </c>
       <c r="D18" s="8">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="E18" s="23" t="s">
         <v>31</v>
@@ -982,7 +982,7 @@
         <v>18</v>
       </c>
       <c r="D19" s="8">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="E19" s="23" t="s">
         <v>28</v>
@@ -999,10 +999,10 @@
         <v>19</v>
       </c>
       <c r="D20" s="8">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:5" s="4" customFormat="1" ht="40.049999999999997" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.4">
